--- a/新点e交易相关材料/项目服务器规划/产品服务器/企业监管平台资源清单.xlsx
+++ b/新点e交易相关材料/项目服务器规划/产品服务器/企业监管平台资源清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24685" windowHeight="11520" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12291" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="最小化清单" sheetId="1" r:id="rId1"/>
@@ -715,13 +715,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF018FFB"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei"/>
@@ -732,18 +744,6 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF00B0F0"/>
-      <name val="Microsoft YaHei"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF018FFB"/>
-      <name val="Helvetica Neue"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1275,7 +1275,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1332,6 +1332,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2007,16 +2010,16 @@
       <c r="A3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>28</v>
       </c>
       <c r="F3" s="14" t="s">
@@ -2025,7 +2028,7 @@
       <c r="G3" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="20" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="12" t="s">
@@ -2096,7 +2099,7 @@
       <c r="G4" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="20" t="s">
         <v>31</v>
       </c>
       <c r="I4" s="12" t="s">
@@ -2141,7 +2144,7 @@
       <c r="A5" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="28" t="s">
         <v>47</v>
       </c>
       <c r="C5" s="13" t="s">
@@ -2202,13 +2205,13 @@
     </row>
     <row r="6" ht="77.25" customHeight="1" spans="1:23">
       <c r="A6" s="18"/>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="20" t="s">
         <v>56</v>
       </c>
       <c r="E6" s="13" t="s">
@@ -2220,7 +2223,7 @@
       <c r="G6" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="20" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="12" t="s">
@@ -2269,7 +2272,7 @@
       <c r="A7" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="28" t="s">
         <v>63</v>
       </c>
       <c r="C7" s="13" t="s">
@@ -2283,7 +2286,7 @@
       <c r="G7" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="20" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="12" t="s">
@@ -2315,8 +2318,8 @@
       <c r="W7" s="14"/>
     </row>
     <row r="8" ht="64.5" customHeight="1" spans="1:23">
-      <c r="A8" s="29"/>
-      <c r="B8" s="27" t="s">
+      <c r="A8" s="30"/>
+      <c r="B8" s="28" t="s">
         <v>66</v>
       </c>
       <c r="C8" s="13" t="s">
@@ -2334,7 +2337,7 @@
       <c r="G8" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="20" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="12" t="s">
@@ -2390,7 +2393,7 @@
       <c r="D9" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="21" t="s">
         <v>74</v>
       </c>
       <c r="F9" s="14" t="s">
@@ -2399,7 +2402,7 @@
       <c r="G9" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="H9" s="20" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="12" t="s">
@@ -2462,7 +2465,7 @@
       <c r="G10" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H10" s="20" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="12" t="s">
@@ -2485,7 +2488,7 @@
         <v>1000</v>
       </c>
       <c r="O10" s="13"/>
-      <c r="P10" s="19">
+      <c r="P10" s="20">
         <v>873</v>
       </c>
       <c r="Q10" s="13"/>
@@ -2524,7 +2527,7 @@
       <c r="G11" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="H11" s="30" t="s">
+      <c r="H11" s="31" t="s">
         <v>84</v>
       </c>
       <c r="I11" s="16" t="s">
@@ -2546,12 +2549,12 @@
       <c r="N11" s="16">
         <v>300</v>
       </c>
-      <c r="O11" s="21"/>
-      <c r="P11" s="21" t="s">
+      <c r="O11" s="22"/>
+      <c r="P11" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="Q11" s="21"/>
-      <c r="R11" s="21"/>
+      <c r="Q11" s="22"/>
+      <c r="R11" s="22"/>
       <c r="S11" s="16">
         <v>1000</v>
       </c>
@@ -2560,546 +2563,546 @@
       <c r="V11" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="W11" s="22" t="s">
+      <c r="W11" s="23" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="12" ht="12.4" spans="1:23">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="32" t="s">
         <v>86</v>
       </c>
       <c r="B12" s="18"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
       <c r="H12" s="18"/>
       <c r="I12" s="18"/>
-      <c r="J12" s="32">
+      <c r="J12" s="33">
         <f>SUM(J3:J11)</f>
         <v>9</v>
       </c>
-      <c r="K12" s="32">
+      <c r="K12" s="33">
         <f>SUM(K3:K11)</f>
         <v>66</v>
       </c>
-      <c r="L12" s="32">
+      <c r="L12" s="33">
         <f>SUM(L3:L11)</f>
         <v>132</v>
       </c>
-      <c r="M12" s="32">
+      <c r="M12" s="33">
         <f>SUM(M3:M11)</f>
         <v>124</v>
       </c>
-      <c r="N12" s="32">
+      <c r="N12" s="33">
         <f>SUM(N3:N11)</f>
         <v>4700</v>
       </c>
-      <c r="O12" s="32"/>
-      <c r="P12" s="32"/>
-      <c r="Q12" s="32"/>
-      <c r="R12" s="32"/>
-      <c r="S12" s="32"/>
-      <c r="T12" s="32"/>
-      <c r="U12" s="32"/>
-      <c r="V12" s="32"/>
-      <c r="W12" s="33"/>
+      <c r="O12" s="33"/>
+      <c r="P12" s="33"/>
+      <c r="Q12" s="33"/>
+      <c r="R12" s="33"/>
+      <c r="S12" s="33"/>
+      <c r="T12" s="33"/>
+      <c r="U12" s="33"/>
+      <c r="V12" s="33"/>
+      <c r="W12" s="34"/>
     </row>
     <row r="13" ht="12.4" spans="1:23">
-      <c r="W13" s="26"/>
+      <c r="W13" s="27"/>
     </row>
     <row r="14" ht="12.4" spans="1:23">
-      <c r="W14" s="26"/>
+      <c r="W14" s="27"/>
     </row>
     <row r="15" ht="12.4" spans="1:23">
-      <c r="W15" s="26"/>
+      <c r="W15" s="27"/>
     </row>
     <row r="16" ht="12.4" spans="1:23">
-      <c r="W16" s="26"/>
+      <c r="W16" s="27"/>
     </row>
     <row r="17" ht="12.4" spans="23:23">
-      <c r="W17" s="26"/>
+      <c r="W17" s="27"/>
     </row>
     <row r="18" ht="12.4" spans="23:23">
-      <c r="W18" s="26"/>
+      <c r="W18" s="27"/>
     </row>
     <row r="19" ht="12.4" spans="23:23">
-      <c r="W19" s="26"/>
+      <c r="W19" s="27"/>
     </row>
     <row r="20" ht="12.4" spans="23:23">
-      <c r="W20" s="26"/>
+      <c r="W20" s="27"/>
     </row>
     <row r="21" ht="12.4" spans="23:23">
-      <c r="W21" s="26"/>
+      <c r="W21" s="27"/>
     </row>
     <row r="22" ht="12.4" spans="23:23">
-      <c r="W22" s="26"/>
+      <c r="W22" s="27"/>
     </row>
     <row r="23" ht="12.4" spans="23:23">
-      <c r="W23" s="26"/>
+      <c r="W23" s="27"/>
     </row>
     <row r="24" ht="12.4" spans="23:23">
-      <c r="W24" s="26"/>
+      <c r="W24" s="27"/>
     </row>
     <row r="25" ht="12.4" spans="23:23">
-      <c r="W25" s="26"/>
+      <c r="W25" s="27"/>
     </row>
     <row r="26" ht="12.4" spans="23:23">
-      <c r="W26" s="26"/>
+      <c r="W26" s="27"/>
     </row>
     <row r="27" ht="12.4" spans="23:23">
-      <c r="W27" s="26"/>
+      <c r="W27" s="27"/>
     </row>
     <row r="28" ht="12.4" spans="23:23">
-      <c r="W28" s="26"/>
+      <c r="W28" s="27"/>
     </row>
     <row r="29" ht="12.4" spans="23:23">
-      <c r="W29" s="26"/>
+      <c r="W29" s="27"/>
     </row>
     <row r="30" ht="12.4" spans="23:23">
-      <c r="W30" s="26"/>
+      <c r="W30" s="27"/>
     </row>
     <row r="31" ht="12.4" spans="23:23">
-      <c r="W31" s="26"/>
+      <c r="W31" s="27"/>
     </row>
     <row r="32" ht="12.4" spans="23:23">
-      <c r="W32" s="26"/>
+      <c r="W32" s="27"/>
     </row>
     <row r="33" ht="12.4" spans="23:23">
-      <c r="W33" s="26"/>
+      <c r="W33" s="27"/>
     </row>
     <row r="34" ht="12.4" spans="23:23">
-      <c r="W34" s="26"/>
+      <c r="W34" s="27"/>
     </row>
     <row r="35" ht="12.4" spans="23:23">
-      <c r="W35" s="26"/>
+      <c r="W35" s="27"/>
     </row>
     <row r="36" ht="12.4" spans="23:23">
-      <c r="W36" s="26"/>
+      <c r="W36" s="27"/>
     </row>
     <row r="37" ht="12.4" spans="23:23">
-      <c r="W37" s="26"/>
+      <c r="W37" s="27"/>
     </row>
     <row r="38" ht="12.4" spans="23:23">
-      <c r="W38" s="26"/>
+      <c r="W38" s="27"/>
     </row>
     <row r="39" ht="12.4" spans="23:23">
-      <c r="W39" s="26"/>
+      <c r="W39" s="27"/>
     </row>
     <row r="40" ht="12.4" spans="23:23">
-      <c r="W40" s="26"/>
+      <c r="W40" s="27"/>
     </row>
     <row r="41" ht="12.4" spans="23:23">
-      <c r="W41" s="26"/>
+      <c r="W41" s="27"/>
     </row>
     <row r="42" ht="12.4" spans="23:23">
-      <c r="W42" s="26"/>
+      <c r="W42" s="27"/>
     </row>
     <row r="43" ht="12.4" spans="23:23">
-      <c r="W43" s="26"/>
+      <c r="W43" s="27"/>
     </row>
     <row r="44" ht="12.4" spans="23:23">
-      <c r="W44" s="26"/>
+      <c r="W44" s="27"/>
     </row>
     <row r="45" ht="12.4" spans="23:23">
-      <c r="W45" s="26"/>
+      <c r="W45" s="27"/>
     </row>
     <row r="46" ht="12.4" spans="23:23">
-      <c r="W46" s="26"/>
+      <c r="W46" s="27"/>
     </row>
     <row r="47" ht="12.4" spans="23:23">
-      <c r="W47" s="26"/>
+      <c r="W47" s="27"/>
     </row>
     <row r="48" ht="12.4" spans="23:23">
-      <c r="W48" s="26"/>
+      <c r="W48" s="27"/>
     </row>
     <row r="49" ht="12.4" spans="23:23">
-      <c r="W49" s="26"/>
+      <c r="W49" s="27"/>
     </row>
     <row r="50" ht="12.4" spans="23:23">
-      <c r="W50" s="26"/>
+      <c r="W50" s="27"/>
     </row>
     <row r="51" ht="12.4" spans="23:23">
-      <c r="W51" s="26"/>
+      <c r="W51" s="27"/>
     </row>
     <row r="52" ht="12.4" spans="23:23">
-      <c r="W52" s="26"/>
+      <c r="W52" s="27"/>
     </row>
     <row r="53" ht="12.4" spans="23:23">
-      <c r="W53" s="26"/>
+      <c r="W53" s="27"/>
     </row>
     <row r="54" ht="12.4" spans="23:23">
-      <c r="W54" s="26"/>
+      <c r="W54" s="27"/>
     </row>
     <row r="55" ht="12.4" spans="23:23">
-      <c r="W55" s="26"/>
+      <c r="W55" s="27"/>
     </row>
     <row r="56" ht="12.4" spans="23:23">
-      <c r="W56" s="26"/>
+      <c r="W56" s="27"/>
     </row>
     <row r="57" ht="12.4" spans="23:23">
-      <c r="W57" s="26"/>
+      <c r="W57" s="27"/>
     </row>
     <row r="58" ht="12.4" spans="23:23">
-      <c r="W58" s="26"/>
+      <c r="W58" s="27"/>
     </row>
     <row r="59" ht="12.4" spans="23:23">
-      <c r="W59" s="26"/>
+      <c r="W59" s="27"/>
     </row>
     <row r="60" ht="12.4" spans="23:23">
-      <c r="W60" s="26"/>
+      <c r="W60" s="27"/>
     </row>
     <row r="61" ht="12.4" spans="23:23">
-      <c r="W61" s="26"/>
+      <c r="W61" s="27"/>
     </row>
     <row r="62" ht="12.4" spans="23:23">
-      <c r="W62" s="26"/>
+      <c r="W62" s="27"/>
     </row>
     <row r="63" ht="12.4" spans="23:23">
-      <c r="W63" s="26"/>
+      <c r="W63" s="27"/>
     </row>
     <row r="64" ht="12.4" spans="23:23">
-      <c r="W64" s="26"/>
+      <c r="W64" s="27"/>
     </row>
     <row r="65" ht="12.4" spans="23:23">
-      <c r="W65" s="26"/>
+      <c r="W65" s="27"/>
     </row>
     <row r="66" ht="12.4" spans="23:23">
-      <c r="W66" s="26"/>
+      <c r="W66" s="27"/>
     </row>
     <row r="67" ht="12.4" spans="23:23">
-      <c r="W67" s="26"/>
+      <c r="W67" s="27"/>
     </row>
     <row r="68" ht="12.4" spans="23:23">
-      <c r="W68" s="26"/>
+      <c r="W68" s="27"/>
     </row>
     <row r="69" ht="12.4" spans="23:23">
-      <c r="W69" s="26"/>
+      <c r="W69" s="27"/>
     </row>
     <row r="70" ht="12.4" spans="23:23">
-      <c r="W70" s="26"/>
+      <c r="W70" s="27"/>
     </row>
     <row r="71" ht="12.4" spans="23:23">
-      <c r="W71" s="26"/>
+      <c r="W71" s="27"/>
     </row>
     <row r="72" ht="12.4" spans="23:23">
-      <c r="W72" s="26"/>
+      <c r="W72" s="27"/>
     </row>
     <row r="73" ht="12.4" spans="23:23">
-      <c r="W73" s="26"/>
+      <c r="W73" s="27"/>
     </row>
     <row r="74" ht="12.4" spans="23:23">
-      <c r="W74" s="26"/>
+      <c r="W74" s="27"/>
     </row>
     <row r="75" ht="12.4" spans="23:23">
-      <c r="W75" s="26"/>
+      <c r="W75" s="27"/>
     </row>
     <row r="76" ht="12.4" spans="23:23">
-      <c r="W76" s="26"/>
+      <c r="W76" s="27"/>
     </row>
     <row r="77" ht="12.4" spans="23:23">
-      <c r="W77" s="26"/>
+      <c r="W77" s="27"/>
     </row>
     <row r="78" ht="12.4" spans="23:23">
-      <c r="W78" s="26"/>
+      <c r="W78" s="27"/>
     </row>
     <row r="79" ht="12.4" spans="23:23">
-      <c r="W79" s="26"/>
+      <c r="W79" s="27"/>
     </row>
     <row r="80" ht="12.4" spans="23:23">
-      <c r="W80" s="26"/>
+      <c r="W80" s="27"/>
     </row>
     <row r="81" ht="12.4" spans="23:23">
-      <c r="W81" s="26"/>
+      <c r="W81" s="27"/>
     </row>
     <row r="82" ht="12.4" spans="23:23">
-      <c r="W82" s="26"/>
+      <c r="W82" s="27"/>
     </row>
     <row r="83" ht="12.4" spans="23:23">
-      <c r="W83" s="26"/>
+      <c r="W83" s="27"/>
     </row>
     <row r="84" ht="12.4" spans="23:23">
-      <c r="W84" s="26"/>
+      <c r="W84" s="27"/>
     </row>
     <row r="85" ht="12.4" spans="23:23">
-      <c r="W85" s="26"/>
+      <c r="W85" s="27"/>
     </row>
     <row r="86" ht="12.4" spans="23:23">
-      <c r="W86" s="26"/>
+      <c r="W86" s="27"/>
     </row>
     <row r="87" ht="12.4" spans="23:23">
-      <c r="W87" s="26"/>
+      <c r="W87" s="27"/>
     </row>
     <row r="88" ht="12.4" spans="23:23">
-      <c r="W88" s="26"/>
+      <c r="W88" s="27"/>
     </row>
     <row r="89" ht="12.4" spans="23:23">
-      <c r="W89" s="26"/>
+      <c r="W89" s="27"/>
     </row>
     <row r="90" ht="12.4" spans="23:23">
-      <c r="W90" s="26"/>
+      <c r="W90" s="27"/>
     </row>
     <row r="91" ht="12.4" spans="23:23">
-      <c r="W91" s="26"/>
+      <c r="W91" s="27"/>
     </row>
     <row r="92" ht="12.4" spans="23:23">
-      <c r="W92" s="26"/>
+      <c r="W92" s="27"/>
     </row>
     <row r="93" ht="12.4" spans="23:23">
-      <c r="W93" s="26"/>
+      <c r="W93" s="27"/>
     </row>
     <row r="94" ht="12.4" spans="23:23">
-      <c r="W94" s="26"/>
+      <c r="W94" s="27"/>
     </row>
     <row r="95" ht="12.4" spans="23:23">
-      <c r="W95" s="26"/>
+      <c r="W95" s="27"/>
     </row>
     <row r="96" ht="12.4" spans="23:23">
-      <c r="W96" s="26"/>
+      <c r="W96" s="27"/>
     </row>
     <row r="97" ht="12.4" spans="23:23">
-      <c r="W97" s="26"/>
+      <c r="W97" s="27"/>
     </row>
     <row r="98" ht="12.4" spans="23:23">
-      <c r="W98" s="26"/>
+      <c r="W98" s="27"/>
     </row>
     <row r="99" ht="12.4" spans="23:23">
-      <c r="W99" s="26"/>
+      <c r="W99" s="27"/>
     </row>
     <row r="100" ht="12.4" spans="23:23">
-      <c r="W100" s="26"/>
+      <c r="W100" s="27"/>
     </row>
     <row r="101" ht="12.4" spans="23:23">
-      <c r="W101" s="26"/>
+      <c r="W101" s="27"/>
     </row>
     <row r="102" ht="12.4" spans="23:23">
-      <c r="W102" s="26"/>
+      <c r="W102" s="27"/>
     </row>
     <row r="103" ht="12.4" spans="23:23">
-      <c r="W103" s="26"/>
+      <c r="W103" s="27"/>
     </row>
     <row r="104" ht="12.4" spans="23:23">
-      <c r="W104" s="26"/>
+      <c r="W104" s="27"/>
     </row>
     <row r="105" ht="12.4" spans="23:23">
-      <c r="W105" s="26"/>
+      <c r="W105" s="27"/>
     </row>
     <row r="106" ht="12.4" spans="23:23">
-      <c r="W106" s="26"/>
+      <c r="W106" s="27"/>
     </row>
     <row r="107" ht="12.4" spans="23:23">
-      <c r="W107" s="26"/>
+      <c r="W107" s="27"/>
     </row>
     <row r="108" ht="12.4" spans="23:23">
-      <c r="W108" s="26"/>
+      <c r="W108" s="27"/>
     </row>
     <row r="109" ht="12.4" spans="23:23">
-      <c r="W109" s="26"/>
+      <c r="W109" s="27"/>
     </row>
     <row r="110" ht="12.4" spans="23:23">
-      <c r="W110" s="26"/>
+      <c r="W110" s="27"/>
     </row>
     <row r="111" ht="12.4" spans="23:23">
-      <c r="W111" s="26"/>
+      <c r="W111" s="27"/>
     </row>
     <row r="112" ht="12.4" spans="23:23">
-      <c r="W112" s="26"/>
+      <c r="W112" s="27"/>
     </row>
     <row r="113" ht="12.4" spans="23:23">
-      <c r="W113" s="26"/>
+      <c r="W113" s="27"/>
     </row>
     <row r="114" ht="12.4" spans="23:23">
-      <c r="W114" s="26"/>
+      <c r="W114" s="27"/>
     </row>
     <row r="115" ht="12.4" spans="23:23">
-      <c r="W115" s="26"/>
+      <c r="W115" s="27"/>
     </row>
     <row r="116" ht="12.4" spans="23:23">
-      <c r="W116" s="26"/>
+      <c r="W116" s="27"/>
     </row>
     <row r="117" ht="12.4" spans="23:23">
-      <c r="W117" s="26"/>
+      <c r="W117" s="27"/>
     </row>
     <row r="118" ht="12.4" spans="23:23">
-      <c r="W118" s="26"/>
+      <c r="W118" s="27"/>
     </row>
     <row r="119" ht="12.4" spans="23:23">
-      <c r="W119" s="26"/>
+      <c r="W119" s="27"/>
     </row>
     <row r="120" ht="12.4" spans="23:23">
-      <c r="W120" s="26"/>
+      <c r="W120" s="27"/>
     </row>
     <row r="121" ht="12.4" spans="23:23">
-      <c r="W121" s="26"/>
+      <c r="W121" s="27"/>
     </row>
     <row r="122" ht="12.4" spans="23:23">
-      <c r="W122" s="26"/>
+      <c r="W122" s="27"/>
     </row>
     <row r="123" ht="12.4" spans="23:23">
-      <c r="W123" s="26"/>
+      <c r="W123" s="27"/>
     </row>
     <row r="124" ht="12.4" spans="23:23">
-      <c r="W124" s="26"/>
+      <c r="W124" s="27"/>
     </row>
     <row r="125" ht="12.4" spans="23:23">
-      <c r="W125" s="26"/>
+      <c r="W125" s="27"/>
     </row>
     <row r="126" ht="12.4" spans="23:23">
-      <c r="W126" s="26"/>
+      <c r="W126" s="27"/>
     </row>
     <row r="127" ht="12.4" spans="23:23">
-      <c r="W127" s="26"/>
+      <c r="W127" s="27"/>
     </row>
     <row r="128" ht="12.4" spans="23:23">
-      <c r="W128" s="26"/>
+      <c r="W128" s="27"/>
     </row>
     <row r="129" ht="12.4" spans="23:23">
-      <c r="W129" s="26"/>
+      <c r="W129" s="27"/>
     </row>
     <row r="130" ht="12.4" spans="23:23">
-      <c r="W130" s="26"/>
+      <c r="W130" s="27"/>
     </row>
     <row r="131" ht="12.4" spans="23:23">
-      <c r="W131" s="26"/>
+      <c r="W131" s="27"/>
     </row>
     <row r="132" ht="12.4" spans="23:23">
-      <c r="W132" s="26"/>
+      <c r="W132" s="27"/>
     </row>
     <row r="133" ht="12.4" spans="23:23">
-      <c r="W133" s="26"/>
+      <c r="W133" s="27"/>
     </row>
     <row r="134" ht="12.4" spans="23:23">
-      <c r="W134" s="26"/>
+      <c r="W134" s="27"/>
     </row>
     <row r="135" ht="12.4" spans="23:23">
-      <c r="W135" s="26"/>
+      <c r="W135" s="27"/>
     </row>
     <row r="136" ht="12.4" spans="23:23">
-      <c r="W136" s="26"/>
+      <c r="W136" s="27"/>
     </row>
     <row r="137" ht="12.4" spans="23:23">
-      <c r="W137" s="26"/>
+      <c r="W137" s="27"/>
     </row>
     <row r="138" ht="12.4" spans="23:23">
-      <c r="W138" s="26"/>
+      <c r="W138" s="27"/>
     </row>
     <row r="139" ht="12.4" spans="23:23">
-      <c r="W139" s="26"/>
+      <c r="W139" s="27"/>
     </row>
     <row r="140" ht="12.4" spans="23:23">
-      <c r="W140" s="26"/>
+      <c r="W140" s="27"/>
     </row>
     <row r="141" ht="12.4" spans="23:23">
-      <c r="W141" s="26"/>
+      <c r="W141" s="27"/>
     </row>
     <row r="142" ht="12.4" spans="23:23">
-      <c r="W142" s="26"/>
+      <c r="W142" s="27"/>
     </row>
     <row r="143" ht="12.4" spans="23:23">
-      <c r="W143" s="26"/>
+      <c r="W143" s="27"/>
     </row>
     <row r="144" ht="12.4" spans="23:23">
-      <c r="W144" s="26"/>
+      <c r="W144" s="27"/>
     </row>
     <row r="145" ht="12.4" spans="23:23">
-      <c r="W145" s="26"/>
+      <c r="W145" s="27"/>
     </row>
     <row r="146" ht="12.4" spans="23:23">
-      <c r="W146" s="26"/>
+      <c r="W146" s="27"/>
     </row>
     <row r="147" ht="12.4" spans="23:23">
-      <c r="W147" s="26"/>
+      <c r="W147" s="27"/>
     </row>
     <row r="148" ht="12.4" spans="23:23">
-      <c r="W148" s="26"/>
+      <c r="W148" s="27"/>
     </row>
     <row r="149" ht="12.4" spans="23:23">
-      <c r="W149" s="26"/>
+      <c r="W149" s="27"/>
     </row>
     <row r="150" ht="12.4" spans="23:23">
-      <c r="W150" s="26"/>
+      <c r="W150" s="27"/>
     </row>
     <row r="151" ht="12.4" spans="23:23">
-      <c r="W151" s="26"/>
+      <c r="W151" s="27"/>
     </row>
     <row r="152" ht="12.4" spans="23:23">
-      <c r="W152" s="26"/>
+      <c r="W152" s="27"/>
     </row>
     <row r="153" ht="12.4" spans="23:23">
-      <c r="W153" s="26"/>
+      <c r="W153" s="27"/>
     </row>
     <row r="154" ht="12.4" spans="23:23">
-      <c r="W154" s="26"/>
+      <c r="W154" s="27"/>
     </row>
     <row r="155" ht="12.4" spans="23:23">
-      <c r="W155" s="26"/>
+      <c r="W155" s="27"/>
     </row>
     <row r="156" ht="12.4" spans="23:23">
-      <c r="W156" s="26"/>
+      <c r="W156" s="27"/>
     </row>
     <row r="157" ht="12.4" spans="23:23">
-      <c r="W157" s="26"/>
+      <c r="W157" s="27"/>
     </row>
     <row r="158" ht="12.4" spans="23:23">
-      <c r="W158" s="26"/>
+      <c r="W158" s="27"/>
     </row>
     <row r="159" ht="12.4" spans="23:23">
-      <c r="W159" s="26"/>
+      <c r="W159" s="27"/>
     </row>
     <row r="160" ht="12.4" spans="23:23">
-      <c r="W160" s="26"/>
+      <c r="W160" s="27"/>
     </row>
     <row r="161" ht="12.4" spans="23:23">
-      <c r="W161" s="26"/>
+      <c r="W161" s="27"/>
     </row>
     <row r="162" ht="12.4" spans="23:23">
-      <c r="W162" s="26"/>
+      <c r="W162" s="27"/>
     </row>
     <row r="163" ht="12.4" spans="23:23">
-      <c r="W163" s="26"/>
+      <c r="W163" s="27"/>
     </row>
     <row r="164" ht="12.4" spans="23:23">
-      <c r="W164" s="26"/>
+      <c r="W164" s="27"/>
     </row>
     <row r="165" ht="12.4" spans="23:23">
-      <c r="W165" s="26"/>
+      <c r="W165" s="27"/>
     </row>
     <row r="166" ht="12.4" spans="23:23">
-      <c r="W166" s="26"/>
+      <c r="W166" s="27"/>
     </row>
     <row r="167" ht="12.4" spans="23:23">
-      <c r="W167" s="26"/>
+      <c r="W167" s="27"/>
     </row>
     <row r="168" ht="12.4" spans="23:23">
-      <c r="W168" s="26"/>
+      <c r="W168" s="27"/>
     </row>
     <row r="169" ht="12.4" spans="23:23">
-      <c r="W169" s="26"/>
+      <c r="W169" s="27"/>
     </row>
     <row r="170" ht="12.4" spans="23:23">
-      <c r="W170" s="26"/>
+      <c r="W170" s="27"/>
     </row>
     <row r="171" ht="12.4" spans="23:23">
-      <c r="W171" s="26"/>
+      <c r="W171" s="27"/>
     </row>
     <row r="172" ht="12.4" spans="23:23">
-      <c r="W172" s="26"/>
+      <c r="W172" s="27"/>
     </row>
     <row r="173" ht="12.4" spans="23:23">
-      <c r="W173" s="26"/>
+      <c r="W173" s="27"/>
     </row>
     <row r="174" ht="12.4" spans="23:23">
-      <c r="W174" s="26"/>
+      <c r="W174" s="27"/>
     </row>
     <row r="175" ht="12.4" spans="23:23">
-      <c r="W175" s="26"/>
+      <c r="W175" s="27"/>
     </row>
     <row r="176" ht="12.4" spans="23:23">
-      <c r="W176" s="26"/>
+      <c r="W176" s="27"/>
     </row>
     <row r="177" ht="12.4" spans="23:23">
-      <c r="W177" s="26"/>
+      <c r="W177" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3438,13 +3441,13 @@
       <c r="B6" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="19" t="s">
         <v>93</v>
       </c>
       <c r="F6" s="14" t="s">
@@ -3568,13 +3571,13 @@
       <c r="B8" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="19" t="s">
         <v>97</v>
       </c>
       <c r="F8" s="14" t="s">
@@ -3632,7 +3635,7 @@
       <c r="G9" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="H9" s="20" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="12" t="s">
@@ -3716,7 +3719,7 @@
       <c r="P10" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="Q10" s="20" t="s">
+      <c r="Q10" s="21" t="s">
         <v>103</v>
       </c>
       <c r="R10" s="13"/>
@@ -3745,7 +3748,7 @@
       <c r="D11" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="21" t="s">
         <v>74</v>
       </c>
       <c r="F11" s="14" t="s">
@@ -3754,7 +3757,7 @@
       <c r="G11" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="19" t="s">
+      <c r="H11" s="20" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="12" t="s">
@@ -3840,7 +3843,7 @@
         <v>1000</v>
       </c>
       <c r="O12" s="13"/>
-      <c r="P12" s="19">
+      <c r="P12" s="20">
         <v>873</v>
       </c>
       <c r="Q12" s="13"/>
@@ -3879,7 +3882,7 @@
       <c r="G13" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="H13" s="21" t="s">
+      <c r="H13" s="22" t="s">
         <v>84</v>
       </c>
       <c r="I13" s="16" t="s">
@@ -3901,12 +3904,12 @@
       <c r="N13" s="16">
         <v>300</v>
       </c>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21" t="s">
+      <c r="O13" s="22"/>
+      <c r="P13" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="Q13" s="21"/>
-      <c r="R13" s="21"/>
+      <c r="Q13" s="22"/>
+      <c r="R13" s="22"/>
       <c r="S13" s="16">
         <v>1000</v>
       </c>
@@ -3915,12 +3918,12 @@
       <c r="V13" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="W13" s="22" t="s">
+      <c r="W13" s="23" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="14" ht="12.4" spans="1:23">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="24" t="s">
         <v>86</v>
       </c>
       <c r="B14" s="18"/>
@@ -3931,590 +3934,590 @@
       <c r="G14" s="18"/>
       <c r="H14" s="18"/>
       <c r="I14" s="18"/>
-      <c r="J14" s="24">
+      <c r="J14" s="25">
         <f>SUM(J3:J13)</f>
         <v>11</v>
       </c>
-      <c r="K14" s="24">
+      <c r="K14" s="25">
         <f>SUM(K3:K13)</f>
         <v>92</v>
       </c>
-      <c r="L14" s="24">
+      <c r="L14" s="25">
         <f>SUM(L3:L13)</f>
         <v>184</v>
       </c>
-      <c r="M14" s="24">
+      <c r="M14" s="25">
         <f>SUM(M3:M13)</f>
         <v>176</v>
       </c>
-      <c r="N14" s="24">
+      <c r="N14" s="25">
         <f>SUM(N3:N13)</f>
         <v>5800</v>
       </c>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="24"/>
-      <c r="U14" s="24"/>
-      <c r="V14" s="24"/>
-      <c r="W14" s="25"/>
+      <c r="O14" s="25"/>
+      <c r="P14" s="25"/>
+      <c r="Q14" s="25"/>
+      <c r="R14" s="25"/>
+      <c r="S14" s="25"/>
+      <c r="T14" s="25"/>
+      <c r="U14" s="25"/>
+      <c r="V14" s="25"/>
+      <c r="W14" s="26"/>
     </row>
     <row r="15" ht="12.4" spans="1:23">
-      <c r="W15" s="26"/>
+      <c r="W15" s="27"/>
     </row>
     <row r="16" ht="12.4" spans="1:23">
-      <c r="W16" s="26"/>
+      <c r="W16" s="27"/>
     </row>
     <row r="17" ht="12.4" spans="23:23">
-      <c r="W17" s="26"/>
+      <c r="W17" s="27"/>
     </row>
     <row r="18" ht="12.4" spans="23:23">
-      <c r="W18" s="26"/>
+      <c r="W18" s="27"/>
     </row>
     <row r="19" ht="12.4" spans="23:23">
-      <c r="W19" s="26"/>
+      <c r="W19" s="27"/>
     </row>
     <row r="20" ht="12.4" spans="23:23">
-      <c r="W20" s="26"/>
+      <c r="W20" s="27"/>
     </row>
     <row r="21" ht="12.4" spans="23:23">
-      <c r="W21" s="26"/>
+      <c r="W21" s="27"/>
     </row>
     <row r="22" ht="12.4" spans="23:23">
-      <c r="W22" s="26"/>
+      <c r="W22" s="27"/>
     </row>
     <row r="23" ht="12.4" spans="23:23">
-      <c r="W23" s="26"/>
+      <c r="W23" s="27"/>
     </row>
     <row r="24" ht="12.4" spans="23:23">
-      <c r="W24" s="26"/>
+      <c r="W24" s="27"/>
     </row>
     <row r="25" ht="12.4" spans="23:23">
-      <c r="W25" s="26"/>
+      <c r="W25" s="27"/>
     </row>
     <row r="26" ht="12.4" spans="23:23">
-      <c r="W26" s="26"/>
+      <c r="W26" s="27"/>
     </row>
     <row r="27" ht="12.4" spans="23:23">
-      <c r="W27" s="26"/>
+      <c r="W27" s="27"/>
     </row>
     <row r="28" ht="12.4" spans="23:23">
-      <c r="W28" s="26"/>
+      <c r="W28" s="27"/>
     </row>
     <row r="29" ht="12.4" spans="23:23">
-      <c r="W29" s="26"/>
+      <c r="W29" s="27"/>
     </row>
     <row r="30" ht="12.4" spans="23:23">
-      <c r="W30" s="26"/>
+      <c r="W30" s="27"/>
     </row>
     <row r="31" ht="12.4" spans="23:23">
-      <c r="W31" s="26"/>
+      <c r="W31" s="27"/>
     </row>
     <row r="32" ht="12.4" spans="23:23">
-      <c r="W32" s="26"/>
+      <c r="W32" s="27"/>
     </row>
     <row r="33" ht="12.4" spans="23:23">
-      <c r="W33" s="26"/>
+      <c r="W33" s="27"/>
     </row>
     <row r="34" ht="12.4" spans="23:23">
-      <c r="W34" s="26"/>
+      <c r="W34" s="27"/>
     </row>
     <row r="35" ht="12.4" spans="23:23">
-      <c r="W35" s="26"/>
+      <c r="W35" s="27"/>
     </row>
     <row r="36" ht="12.4" spans="23:23">
-      <c r="W36" s="26"/>
+      <c r="W36" s="27"/>
     </row>
     <row r="37" ht="12.4" spans="23:23">
-      <c r="W37" s="26"/>
+      <c r="W37" s="27"/>
     </row>
     <row r="38" ht="12.4" spans="23:23">
-      <c r="W38" s="26"/>
+      <c r="W38" s="27"/>
     </row>
     <row r="39" ht="12.4" spans="23:23">
-      <c r="W39" s="26"/>
+      <c r="W39" s="27"/>
     </row>
     <row r="40" ht="12.4" spans="23:23">
-      <c r="W40" s="26"/>
+      <c r="W40" s="27"/>
     </row>
     <row r="41" ht="12.4" spans="23:23">
-      <c r="W41" s="26"/>
+      <c r="W41" s="27"/>
     </row>
     <row r="42" ht="12.4" spans="23:23">
-      <c r="W42" s="26"/>
+      <c r="W42" s="27"/>
     </row>
     <row r="43" ht="12.4" spans="23:23">
-      <c r="W43" s="26"/>
+      <c r="W43" s="27"/>
     </row>
     <row r="44" ht="12.4" spans="23:23">
-      <c r="W44" s="26"/>
+      <c r="W44" s="27"/>
     </row>
     <row r="45" ht="12.4" spans="23:23">
-      <c r="W45" s="26"/>
+      <c r="W45" s="27"/>
     </row>
     <row r="46" ht="12.4" spans="23:23">
-      <c r="W46" s="26"/>
+      <c r="W46" s="27"/>
     </row>
     <row r="47" ht="12.4" spans="23:23">
-      <c r="W47" s="26"/>
+      <c r="W47" s="27"/>
     </row>
     <row r="48" ht="12.4" spans="23:23">
-      <c r="W48" s="26"/>
+      <c r="W48" s="27"/>
     </row>
     <row r="49" ht="12.4" spans="23:23">
-      <c r="W49" s="26"/>
+      <c r="W49" s="27"/>
     </row>
     <row r="50" ht="12.4" spans="23:23">
-      <c r="W50" s="26"/>
+      <c r="W50" s="27"/>
     </row>
     <row r="51" ht="12.4" spans="23:23">
-      <c r="W51" s="26"/>
+      <c r="W51" s="27"/>
     </row>
     <row r="52" ht="12.4" spans="23:23">
-      <c r="W52" s="26"/>
+      <c r="W52" s="27"/>
     </row>
     <row r="53" ht="12.4" spans="23:23">
-      <c r="W53" s="26"/>
+      <c r="W53" s="27"/>
     </row>
     <row r="54" ht="12.4" spans="23:23">
-      <c r="W54" s="26"/>
+      <c r="W54" s="27"/>
     </row>
     <row r="55" ht="12.4" spans="23:23">
-      <c r="W55" s="26"/>
+      <c r="W55" s="27"/>
     </row>
     <row r="56" ht="12.4" spans="23:23">
-      <c r="W56" s="26"/>
+      <c r="W56" s="27"/>
     </row>
     <row r="57" ht="12.4" spans="23:23">
-      <c r="W57" s="26"/>
+      <c r="W57" s="27"/>
     </row>
     <row r="58" ht="12.4" spans="23:23">
-      <c r="W58" s="26"/>
+      <c r="W58" s="27"/>
     </row>
     <row r="59" ht="12.4" spans="23:23">
-      <c r="W59" s="26"/>
+      <c r="W59" s="27"/>
     </row>
     <row r="60" ht="12.4" spans="23:23">
-      <c r="W60" s="26"/>
+      <c r="W60" s="27"/>
     </row>
     <row r="61" ht="12.4" spans="23:23">
-      <c r="W61" s="26"/>
+      <c r="W61" s="27"/>
     </row>
     <row r="62" ht="12.4" spans="23:23">
-      <c r="W62" s="26"/>
+      <c r="W62" s="27"/>
     </row>
     <row r="63" ht="12.4" spans="23:23">
-      <c r="W63" s="26"/>
+      <c r="W63" s="27"/>
     </row>
     <row r="64" ht="12.4" spans="23:23">
-      <c r="W64" s="26"/>
+      <c r="W64" s="27"/>
     </row>
     <row r="65" ht="12.4" spans="23:23">
-      <c r="W65" s="26"/>
+      <c r="W65" s="27"/>
     </row>
     <row r="66" ht="12.4" spans="23:23">
-      <c r="W66" s="26"/>
+      <c r="W66" s="27"/>
     </row>
     <row r="67" ht="12.4" spans="23:23">
-      <c r="W67" s="26"/>
+      <c r="W67" s="27"/>
     </row>
     <row r="68" ht="12.4" spans="23:23">
-      <c r="W68" s="26"/>
+      <c r="W68" s="27"/>
     </row>
     <row r="69" ht="12.4" spans="23:23">
-      <c r="W69" s="26"/>
+      <c r="W69" s="27"/>
     </row>
     <row r="70" ht="12.4" spans="23:23">
-      <c r="W70" s="26"/>
+      <c r="W70" s="27"/>
     </row>
     <row r="71" ht="12.4" spans="23:23">
-      <c r="W71" s="26"/>
+      <c r="W71" s="27"/>
     </row>
     <row r="72" ht="12.4" spans="23:23">
-      <c r="W72" s="26"/>
+      <c r="W72" s="27"/>
     </row>
     <row r="73" ht="12.4" spans="23:23">
-      <c r="W73" s="26"/>
+      <c r="W73" s="27"/>
     </row>
     <row r="74" ht="12.4" spans="23:23">
-      <c r="W74" s="26"/>
+      <c r="W74" s="27"/>
     </row>
     <row r="75" ht="12.4" spans="23:23">
-      <c r="W75" s="26"/>
+      <c r="W75" s="27"/>
     </row>
     <row r="76" ht="12.4" spans="23:23">
-      <c r="W76" s="26"/>
+      <c r="W76" s="27"/>
     </row>
     <row r="77" ht="12.4" spans="23:23">
-      <c r="W77" s="26"/>
+      <c r="W77" s="27"/>
     </row>
     <row r="78" ht="12.4" spans="23:23">
-      <c r="W78" s="26"/>
+      <c r="W78" s="27"/>
     </row>
     <row r="79" ht="12.4" spans="23:23">
-      <c r="W79" s="26"/>
+      <c r="W79" s="27"/>
     </row>
     <row r="80" ht="12.4" spans="23:23">
-      <c r="W80" s="26"/>
+      <c r="W80" s="27"/>
     </row>
     <row r="81" ht="12.4" spans="23:23">
-      <c r="W81" s="26"/>
+      <c r="W81" s="27"/>
     </row>
     <row r="82" ht="12.4" spans="23:23">
-      <c r="W82" s="26"/>
+      <c r="W82" s="27"/>
     </row>
     <row r="83" ht="12.4" spans="23:23">
-      <c r="W83" s="26"/>
+      <c r="W83" s="27"/>
     </row>
     <row r="84" ht="12.4" spans="23:23">
-      <c r="W84" s="26"/>
+      <c r="W84" s="27"/>
     </row>
     <row r="85" ht="12.4" spans="23:23">
-      <c r="W85" s="26"/>
+      <c r="W85" s="27"/>
     </row>
     <row r="86" ht="12.4" spans="23:23">
-      <c r="W86" s="26"/>
+      <c r="W86" s="27"/>
     </row>
     <row r="87" ht="12.4" spans="23:23">
-      <c r="W87" s="26"/>
+      <c r="W87" s="27"/>
     </row>
     <row r="88" ht="12.4" spans="23:23">
-      <c r="W88" s="26"/>
+      <c r="W88" s="27"/>
     </row>
     <row r="89" ht="12.4" spans="23:23">
-      <c r="W89" s="26"/>
+      <c r="W89" s="27"/>
     </row>
     <row r="90" ht="12.4" spans="23:23">
-      <c r="W90" s="26"/>
+      <c r="W90" s="27"/>
     </row>
     <row r="91" ht="12.4" spans="23:23">
-      <c r="W91" s="26"/>
+      <c r="W91" s="27"/>
     </row>
     <row r="92" ht="12.4" spans="23:23">
-      <c r="W92" s="26"/>
+      <c r="W92" s="27"/>
     </row>
     <row r="93" ht="12.4" spans="23:23">
-      <c r="W93" s="26"/>
+      <c r="W93" s="27"/>
     </row>
     <row r="94" ht="12.4" spans="23:23">
-      <c r="W94" s="26"/>
+      <c r="W94" s="27"/>
     </row>
     <row r="95" ht="12.4" spans="23:23">
-      <c r="W95" s="26"/>
+      <c r="W95" s="27"/>
     </row>
     <row r="96" ht="12.4" spans="23:23">
-      <c r="W96" s="26"/>
+      <c r="W96" s="27"/>
     </row>
     <row r="97" ht="12.4" spans="23:23">
-      <c r="W97" s="26"/>
+      <c r="W97" s="27"/>
     </row>
     <row r="98" ht="12.4" spans="23:23">
-      <c r="W98" s="26"/>
+      <c r="W98" s="27"/>
     </row>
     <row r="99" ht="12.4" spans="23:23">
-      <c r="W99" s="26"/>
+      <c r="W99" s="27"/>
     </row>
     <row r="100" ht="12.4" spans="23:23">
-      <c r="W100" s="26"/>
+      <c r="W100" s="27"/>
     </row>
     <row r="101" ht="12.4" spans="23:23">
-      <c r="W101" s="26"/>
+      <c r="W101" s="27"/>
     </row>
     <row r="102" ht="12.4" spans="23:23">
-      <c r="W102" s="26"/>
+      <c r="W102" s="27"/>
     </row>
     <row r="103" ht="12.4" spans="23:23">
-      <c r="W103" s="26"/>
+      <c r="W103" s="27"/>
     </row>
     <row r="104" ht="12.4" spans="23:23">
-      <c r="W104" s="26"/>
+      <c r="W104" s="27"/>
     </row>
     <row r="105" ht="12.4" spans="23:23">
-      <c r="W105" s="26"/>
+      <c r="W105" s="27"/>
     </row>
     <row r="106" ht="12.4" spans="23:23">
-      <c r="W106" s="26"/>
+      <c r="W106" s="27"/>
     </row>
     <row r="107" ht="12.4" spans="23:23">
-      <c r="W107" s="26"/>
+      <c r="W107" s="27"/>
     </row>
     <row r="108" ht="12.4" spans="23:23">
-      <c r="W108" s="26"/>
+      <c r="W108" s="27"/>
     </row>
     <row r="109" ht="12.4" spans="23:23">
-      <c r="W109" s="26"/>
+      <c r="W109" s="27"/>
     </row>
     <row r="110" ht="12.4" spans="23:23">
-      <c r="W110" s="26"/>
+      <c r="W110" s="27"/>
     </row>
     <row r="111" ht="12.4" spans="23:23">
-      <c r="W111" s="26"/>
+      <c r="W111" s="27"/>
     </row>
     <row r="112" ht="12.4" spans="23:23">
-      <c r="W112" s="26"/>
+      <c r="W112" s="27"/>
     </row>
     <row r="113" ht="12.4" spans="23:23">
-      <c r="W113" s="26"/>
+      <c r="W113" s="27"/>
     </row>
     <row r="114" ht="12.4" spans="23:23">
-      <c r="W114" s="26"/>
+      <c r="W114" s="27"/>
     </row>
     <row r="115" ht="12.4" spans="23:23">
-      <c r="W115" s="26"/>
+      <c r="W115" s="27"/>
     </row>
     <row r="116" ht="12.4" spans="23:23">
-      <c r="W116" s="26"/>
+      <c r="W116" s="27"/>
     </row>
     <row r="117" ht="12.4" spans="23:23">
-      <c r="W117" s="26"/>
+      <c r="W117" s="27"/>
     </row>
     <row r="118" ht="12.4" spans="23:23">
-      <c r="W118" s="26"/>
+      <c r="W118" s="27"/>
     </row>
     <row r="119" ht="12.4" spans="23:23">
-      <c r="W119" s="26"/>
+      <c r="W119" s="27"/>
     </row>
     <row r="120" ht="12.4" spans="23:23">
-      <c r="W120" s="26"/>
+      <c r="W120" s="27"/>
     </row>
     <row r="121" ht="12.4" spans="23:23">
-      <c r="W121" s="26"/>
+      <c r="W121" s="27"/>
     </row>
     <row r="122" ht="12.4" spans="23:23">
-      <c r="W122" s="26"/>
+      <c r="W122" s="27"/>
     </row>
     <row r="123" ht="12.4" spans="23:23">
-      <c r="W123" s="26"/>
+      <c r="W123" s="27"/>
     </row>
     <row r="124" ht="12.4" spans="23:23">
-      <c r="W124" s="26"/>
+      <c r="W124" s="27"/>
     </row>
     <row r="125" ht="12.4" spans="23:23">
-      <c r="W125" s="26"/>
+      <c r="W125" s="27"/>
     </row>
     <row r="126" ht="12.4" spans="23:23">
-      <c r="W126" s="26"/>
+      <c r="W126" s="27"/>
     </row>
     <row r="127" ht="12.4" spans="23:23">
-      <c r="W127" s="26"/>
+      <c r="W127" s="27"/>
     </row>
     <row r="128" ht="12.4" spans="23:23">
-      <c r="W128" s="26"/>
+      <c r="W128" s="27"/>
     </row>
     <row r="129" ht="12.4" spans="23:23">
-      <c r="W129" s="26"/>
+      <c r="W129" s="27"/>
     </row>
     <row r="130" ht="12.4" spans="23:23">
-      <c r="W130" s="26"/>
+      <c r="W130" s="27"/>
     </row>
     <row r="131" ht="12.4" spans="23:23">
-      <c r="W131" s="26"/>
+      <c r="W131" s="27"/>
     </row>
     <row r="132" ht="12.4" spans="23:23">
-      <c r="W132" s="26"/>
+      <c r="W132" s="27"/>
     </row>
     <row r="133" ht="12.4" spans="23:23">
-      <c r="W133" s="26"/>
+      <c r="W133" s="27"/>
     </row>
     <row r="134" ht="12.4" spans="23:23">
-      <c r="W134" s="26"/>
+      <c r="W134" s="27"/>
     </row>
     <row r="135" ht="12.4" spans="23:23">
-      <c r="W135" s="26"/>
+      <c r="W135" s="27"/>
     </row>
     <row r="136" ht="12.4" spans="23:23">
-      <c r="W136" s="26"/>
+      <c r="W136" s="27"/>
     </row>
     <row r="137" ht="12.4" spans="23:23">
-      <c r="W137" s="26"/>
+      <c r="W137" s="27"/>
     </row>
     <row r="138" ht="12.4" spans="23:23">
-      <c r="W138" s="26"/>
+      <c r="W138" s="27"/>
     </row>
     <row r="139" ht="12.4" spans="23:23">
-      <c r="W139" s="26"/>
+      <c r="W139" s="27"/>
     </row>
     <row r="140" ht="12.4" spans="23:23">
-      <c r="W140" s="26"/>
+      <c r="W140" s="27"/>
     </row>
     <row r="141" ht="12.4" spans="23:23">
-      <c r="W141" s="26"/>
+      <c r="W141" s="27"/>
     </row>
     <row r="142" ht="12.4" spans="23:23">
-      <c r="W142" s="26"/>
+      <c r="W142" s="27"/>
     </row>
     <row r="143" ht="12.4" spans="23:23">
-      <c r="W143" s="26"/>
+      <c r="W143" s="27"/>
     </row>
     <row r="144" ht="12.4" spans="23:23">
-      <c r="W144" s="26"/>
+      <c r="W144" s="27"/>
     </row>
     <row r="145" ht="12.4" spans="23:23">
-      <c r="W145" s="26"/>
+      <c r="W145" s="27"/>
     </row>
     <row r="146" ht="12.4" spans="23:23">
-      <c r="W146" s="26"/>
+      <c r="W146" s="27"/>
     </row>
     <row r="147" ht="12.4" spans="23:23">
-      <c r="W147" s="26"/>
+      <c r="W147" s="27"/>
     </row>
     <row r="148" ht="12.4" spans="23:23">
-      <c r="W148" s="26"/>
+      <c r="W148" s="27"/>
     </row>
     <row r="149" ht="12.4" spans="23:23">
-      <c r="W149" s="26"/>
+      <c r="W149" s="27"/>
     </row>
     <row r="150" ht="12.4" spans="23:23">
-      <c r="W150" s="26"/>
+      <c r="W150" s="27"/>
     </row>
     <row r="151" ht="12.4" spans="23:23">
-      <c r="W151" s="26"/>
+      <c r="W151" s="27"/>
     </row>
     <row r="152" ht="12.4" spans="23:23">
-      <c r="W152" s="26"/>
+      <c r="W152" s="27"/>
     </row>
     <row r="153" ht="12.4" spans="23:23">
-      <c r="W153" s="26"/>
+      <c r="W153" s="27"/>
     </row>
     <row r="154" ht="12.4" spans="23:23">
-      <c r="W154" s="26"/>
+      <c r="W154" s="27"/>
     </row>
     <row r="155" ht="12.4" spans="23:23">
-      <c r="W155" s="26"/>
+      <c r="W155" s="27"/>
     </row>
     <row r="156" ht="12.4" spans="23:23">
-      <c r="W156" s="26"/>
+      <c r="W156" s="27"/>
     </row>
     <row r="157" ht="12.4" spans="23:23">
-      <c r="W157" s="26"/>
+      <c r="W157" s="27"/>
     </row>
     <row r="158" ht="12.4" spans="23:23">
-      <c r="W158" s="26"/>
+      <c r="W158" s="27"/>
     </row>
     <row r="159" ht="12.4" spans="23:23">
-      <c r="W159" s="26"/>
+      <c r="W159" s="27"/>
     </row>
     <row r="160" ht="12.4" spans="23:23">
-      <c r="W160" s="26"/>
+      <c r="W160" s="27"/>
     </row>
     <row r="161" ht="12.4" spans="23:23">
-      <c r="W161" s="26"/>
+      <c r="W161" s="27"/>
     </row>
     <row r="162" ht="12.4" spans="23:23">
-      <c r="W162" s="26"/>
+      <c r="W162" s="27"/>
     </row>
     <row r="163" ht="12.4" spans="23:23">
-      <c r="W163" s="26"/>
+      <c r="W163" s="27"/>
     </row>
     <row r="164" ht="12.4" spans="23:23">
-      <c r="W164" s="26"/>
+      <c r="W164" s="27"/>
     </row>
     <row r="165" ht="12.4" spans="23:23">
-      <c r="W165" s="26"/>
+      <c r="W165" s="27"/>
     </row>
     <row r="166" ht="12.4" spans="23:23">
-      <c r="W166" s="26"/>
+      <c r="W166" s="27"/>
     </row>
     <row r="167" ht="12.4" spans="23:23">
-      <c r="W167" s="26"/>
+      <c r="W167" s="27"/>
     </row>
     <row r="168" ht="12.4" spans="23:23">
-      <c r="W168" s="26"/>
+      <c r="W168" s="27"/>
     </row>
     <row r="169" ht="12.4" spans="23:23">
-      <c r="W169" s="26"/>
+      <c r="W169" s="27"/>
     </row>
     <row r="170" ht="12.4" spans="23:23">
-      <c r="W170" s="26"/>
+      <c r="W170" s="27"/>
     </row>
     <row r="171" ht="12.4" spans="23:23">
-      <c r="W171" s="26"/>
+      <c r="W171" s="27"/>
     </row>
     <row r="172" ht="12.4" spans="23:23">
-      <c r="W172" s="26"/>
+      <c r="W172" s="27"/>
     </row>
     <row r="173" ht="12.4" spans="23:23">
-      <c r="W173" s="26"/>
+      <c r="W173" s="27"/>
     </row>
     <row r="174" ht="12.4" spans="23:23">
-      <c r="W174" s="26"/>
+      <c r="W174" s="27"/>
     </row>
     <row r="175" ht="12.4" spans="23:23">
-      <c r="W175" s="26"/>
+      <c r="W175" s="27"/>
     </row>
     <row r="176" ht="12.4" spans="23:23">
-      <c r="W176" s="26"/>
+      <c r="W176" s="27"/>
     </row>
     <row r="177" ht="12.4" spans="23:23">
-      <c r="W177" s="26"/>
+      <c r="W177" s="27"/>
     </row>
     <row r="178" ht="12.4" spans="23:23">
-      <c r="W178" s="26"/>
+      <c r="W178" s="27"/>
     </row>
     <row r="179" ht="12.4" spans="23:23">
-      <c r="W179" s="26"/>
+      <c r="W179" s="27"/>
     </row>
     <row r="180" ht="12.4" spans="23:23">
-      <c r="W180" s="26"/>
+      <c r="W180" s="27"/>
     </row>
     <row r="181" ht="12.4" spans="23:23">
-      <c r="W181" s="26"/>
+      <c r="W181" s="27"/>
     </row>
     <row r="182" ht="12.4" spans="23:23">
-      <c r="W182" s="26"/>
+      <c r="W182" s="27"/>
     </row>
     <row r="183" ht="12.4" spans="23:23">
-      <c r="W183" s="26"/>
+      <c r="W183" s="27"/>
     </row>
     <row r="184" ht="12.4" spans="23:23">
-      <c r="W184" s="26"/>
+      <c r="W184" s="27"/>
     </row>
     <row r="185" ht="12.4" spans="23:23">
-      <c r="W185" s="26"/>
+      <c r="W185" s="27"/>
     </row>
     <row r="186" ht="12.4" spans="23:23">
-      <c r="W186" s="26"/>
+      <c r="W186" s="27"/>
     </row>
     <row r="187" ht="12.4" spans="23:23">
-      <c r="W187" s="26"/>
+      <c r="W187" s="27"/>
     </row>
     <row r="188" ht="12.4" spans="23:23">
-      <c r="W188" s="26"/>
+      <c r="W188" s="27"/>
     </row>
     <row r="189" ht="12.4" spans="23:23">
-      <c r="W189" s="26"/>
+      <c r="W189" s="27"/>
     </row>
     <row r="190" ht="12.4" spans="23:23">
-      <c r="W190" s="26"/>
+      <c r="W190" s="27"/>
     </row>
     <row r="191" ht="12.4" spans="23:23">
-      <c r="W191" s="26"/>
+      <c r="W191" s="27"/>
     </row>
     <row r="192" ht="12.4" spans="23:23">
-      <c r="W192" s="26"/>
+      <c r="W192" s="27"/>
     </row>
     <row r="193" ht="12.4" spans="23:23">
-      <c r="W193" s="26"/>
+      <c r="W193" s="27"/>
     </row>
     <row r="194" ht="12.4" spans="23:23">
-      <c r="W194" s="26"/>
+      <c r="W194" s="27"/>
     </row>
     <row r="195" ht="12.4" spans="23:23">
-      <c r="W195" s="26"/>
+      <c r="W195" s="27"/>
     </row>
     <row r="196" ht="12.4" spans="23:23">
-      <c r="W196" s="26"/>
+      <c r="W196" s="27"/>
     </row>
     <row r="197" ht="12.4" spans="23:23">
-      <c r="W197" s="26"/>
+      <c r="W197" s="27"/>
     </row>
     <row r="198" ht="12.4" spans="23:23">
-      <c r="W198" s="26"/>
+      <c r="W198" s="27"/>
     </row>
     <row r="199" ht="12.4" spans="23:23">
-      <c r="W199" s="26"/>
+      <c r="W199" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/新点e交易相关材料/项目服务器规划/产品服务器/企业监管平台资源清单.xlsx
+++ b/新点e交易相关材料/项目服务器规划/产品服务器/企业监管平台资源清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12291" activeTab="1"/>
+    <workbookView windowWidth="27951" windowHeight="12291" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="最小化清单" sheetId="1" r:id="rId1"/>
@@ -721,19 +721,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF018FFB"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-    </font>
-    <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei"/>
@@ -744,6 +738,12 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF018FFB"/>
+      <name val="Helvetica Neue"/>
       <charset val="134"/>
     </font>
   </fonts>
